--- a/server/data/cheque/QBO-Cheque.xlsx
+++ b/server/data/cheque/QBO-Cheque.xlsx
@@ -1,35 +1,283 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="135" windowWidth="20115" windowHeight="7245"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="customers" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+  <si>
+    <t>TxnID</t>
+  </si>
+  <si>
+    <t>TimeCreated</t>
+  </si>
+  <si>
+    <t>TimeModified</t>
+  </si>
+  <si>
+    <t>EditSequence</t>
+  </si>
+  <si>
+    <t>TxnNumber</t>
+  </si>
+  <si>
+    <t>AccountRefListID</t>
+  </si>
+  <si>
+    <t>AccountRefFullName</t>
+  </si>
+  <si>
+    <t>DepartmentRefListID</t>
+  </si>
+  <si>
+    <t>DepartmentRefFullName</t>
+  </si>
+  <si>
+    <t>CurrencyRefListID</t>
+  </si>
+  <si>
+    <t>CurrencyRefFullName</t>
+  </si>
+  <si>
+    <t>ExchangeRate</t>
+  </si>
+  <si>
+    <t>PayeeEntityRefListID</t>
+  </si>
+  <si>
+    <t>PayeeEntityRefFullName</t>
+  </si>
+  <si>
+    <t>RefNumber</t>
+  </si>
+  <si>
+    <t>TxnDate</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Memo</t>
+  </si>
+  <si>
+    <t>AddressAddr1</t>
+  </si>
+  <si>
+    <t>AddressAddr2</t>
+  </si>
+  <si>
+    <t>AddressAddr3</t>
+  </si>
+  <si>
+    <t>AddressAddr4</t>
+  </si>
+  <si>
+    <t>AddressAddr5</t>
+  </si>
+  <si>
+    <t>AddressCity</t>
+  </si>
+  <si>
+    <t>AddressState</t>
+  </si>
+  <si>
+    <t>AddressPostalCode</t>
+  </si>
+  <si>
+    <t>AddressCountry</t>
+  </si>
+  <si>
+    <t>AddressNote</t>
+  </si>
+  <si>
+    <t>IsToBePrinted</t>
+  </si>
+  <si>
+    <t>GlobalTaxCalculation</t>
+  </si>
+  <si>
+    <t>ExpenseLineClearExpenseLines</t>
+  </si>
+  <si>
+    <t>ExpenseLineSeqNo</t>
+  </si>
+  <si>
+    <t>ExpenseLineTxnLineID</t>
+  </si>
+  <si>
+    <t>ExpenseLineMemo</t>
+  </si>
+  <si>
+    <t>ExpenseLineClassRefListID</t>
+  </si>
+  <si>
+    <t>ExpenseLineClassRefFullName</t>
+  </si>
+  <si>
+    <t>ExpenseLineAmount</t>
+  </si>
+  <si>
+    <t>ExpenseLineTaxAmount</t>
+  </si>
+  <si>
+    <t>ExpenseLineIsTaxable</t>
+  </si>
+  <si>
+    <t>ExpenseLineAccountRefListID</t>
+  </si>
+  <si>
+    <t>ExpenseLineAccountRefFullName</t>
+  </si>
+  <si>
+    <t>ExpenseLineCustomerRefListID</t>
+  </si>
+  <si>
+    <t>ExpenseLineCustomerRefFullName</t>
+  </si>
+  <si>
+    <t>ExpenseLineTaxCodeRefListID</t>
+  </si>
+  <si>
+    <t>ExpenseLineTaxCodeRefFullName</t>
+  </si>
+  <si>
+    <t>ExpenseLineBillableStatus</t>
+  </si>
+  <si>
+    <t>ExpenseLineMarkupInfoPercent</t>
+  </si>
+  <si>
+    <t>ExpenseLineMarkupInfoPercentBased</t>
+  </si>
+  <si>
+    <t>ExpenseLineMarkupInfoPriceLevelRefListID</t>
+  </si>
+  <si>
+    <t>ExpenseLineMarkupInfoPriceLevelRefFullName</t>
+  </si>
+  <si>
+    <t>ExpenseLineMarkupInfoValue</t>
+  </si>
+  <si>
+    <t>ExpenseLineTaxInclusiveAmount</t>
+  </si>
+  <si>
+    <t>FQSaveToCache</t>
+  </si>
+  <si>
+    <t>FQPrimaryKey</t>
+  </si>
+  <si>
+    <t>1843</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>FNB Cheque</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ZAR</t>
+  </si>
+  <si>
+    <t>South African Rand</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>ACTSYS Cable &amp; Wireless Solutions</t>
+  </si>
+  <si>
+    <t>FNB OB 000000917 ACTSYS</t>
+  </si>
+  <si>
+    <t>Unit 7 Cedar Park</t>
+  </si>
+  <si>
+    <t>21 Quarry Park Close</t>
+  </si>
+  <si>
+    <t>Riverhorse Valley</t>
+  </si>
+  <si>
+    <t>TaxInclusive</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Accounts Payable (A/P)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Out of Scope</t>
+  </si>
+  <si>
+    <t>NotBillable</t>
+  </si>
+  <si>
+    <t>1843|1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -37,24 +285,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_Sheet2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -205,16 +494,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -336,56 +629,415 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:BB2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="22.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="27.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="31.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="29.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="33" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="24.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="30" style="2" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="35.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="40.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="44.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="30.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="4">
+        <v>44715.509016203701</v>
+      </c>
+      <c r="C2" s="4">
+        <v>44718.247048611112</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1843</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="4">
+        <v>44715</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>8705.7999999999993</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK2" s="5">
+        <v>8705.7999999999993</v>
+      </c>
+      <c r="AL2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="5">
+        <v>8705</v>
+      </c>
+      <c r="BA2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>